--- a/public/sap-reporting/expansion-150-downloads/EXT-MM20-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-MM20-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R539951b0518d485d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Reab526435ae44990"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rb0b97dd15b2842da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R3d3cdd27cca74603"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rf06732446cb945bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R01f1c5173ef04384"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -494,7 +494,7 @@
         <x:v>100.00</x:v>
       </x:c>
       <x:c r="K7" s="2" t="str">
-        <x:v>0000100001</x:v>
+        <x:v>100.00</x:v>
       </x:c>
       <x:c r="L7" s="2" t="str">
         <x:v>EA</x:v>
@@ -545,7 +545,7 @@
         <x:v>125.00</x:v>
       </x:c>
       <x:c r="K8" s="2" t="str">
-        <x:v>0000100002</x:v>
+        <x:v>125.00</x:v>
       </x:c>
       <x:c r="L8" s="2" t="str">
         <x:v>EA</x:v>
@@ -598,7 +598,7 @@
         <x:v>1.234,50</x:v>
       </x:c>
       <x:c r="K9" s="2" t="str">
-        <x:v>0000100003</x:v>
+        <x:v>1.234,50</x:v>
       </x:c>
       <x:c r="L9" s="2" t="str">
         <x:v>EA</x:v>
@@ -651,7 +651,7 @@
         <x:v>175.00</x:v>
       </x:c>
       <x:c r="K10" s="2" t="str">
-        <x:v>0000100004</x:v>
+        <x:v>175.00</x:v>
       </x:c>
       <x:c r="L10" s="2" t="str">
         <x:v>EA</x:v>
@@ -795,7 +795,7 @@
         <x:v>100.00</x:v>
       </x:c>
       <x:c r="K2" s="2" t="str">
-        <x:v>0000100001</x:v>
+        <x:v>100.00</x:v>
       </x:c>
       <x:c r="L2" s="2" t="str">
         <x:v>EA</x:v>
@@ -846,7 +846,7 @@
         <x:v>125.00</x:v>
       </x:c>
       <x:c r="K3" s="2" t="str">
-        <x:v>0000100002</x:v>
+        <x:v>125.00</x:v>
       </x:c>
       <x:c r="L3" s="2" t="str">
         <x:v>EA</x:v>
@@ -899,7 +899,7 @@
         <x:v>1.234,50</x:v>
       </x:c>
       <x:c r="K4" s="2" t="str">
-        <x:v>0000100003</x:v>
+        <x:v>1.234,50</x:v>
       </x:c>
       <x:c r="L4" s="2" t="str">
         <x:v>EA</x:v>
@@ -952,7 +952,7 @@
         <x:v>175.00</x:v>
       </x:c>
       <x:c r="K5" s="2" t="str">
-        <x:v>0000100004</x:v>
+        <x:v>175.00</x:v>
       </x:c>
       <x:c r="L5" s="2" t="str">
         <x:v>EA</x:v>
@@ -1213,7 +1213,7 @@
         <x:v>Giữ chuỗi RAW và locale. Chuẩn hóa dấu, separator, currency/UoM/price unit trước tính. Blank không là0; không cộng tỷ lệ/đơn giá/snapshot.</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="63" customHeight="1">
+    <x:row r="12" ht="80" customHeight="1">
       <x:c r="A12" s="8" t="str">
         <x:v>11</x:v>
       </x:c>
@@ -1221,7 +1221,7 @@
         <x:v>Quota Rating</x:v>
       </x:c>
       <x:c r="C12" s="8" t="str">
-        <x:v>text</x:v>
+        <x:v>raw_decimal</x:v>
       </x:c>
       <x:c r="D12" s="8" t="str">
         <x:v>Thuộc tính nghiệp vụ: Quota Rating. Đọc tại grain của hồ sơ; nhãn và semantics cần đối chiếu hệ công ty.</x:v>
@@ -1230,7 +1230,7 @@
         <x:v>SAVA_PROPOSED / chưa xác minh</x:v>
       </x:c>
       <x:c r="F12" s="8" t="str">
-        <x:v>Giữ ID dạng Text và số0 đầu. Trim trên bản CLEAN riêng, giữ raw value và source-row lineage. Không join bằng tên diễn giải.</x:v>
+        <x:v>Giữ chuỗi RAW và locale. Chuẩn hóa dấu, separator, currency/UoM/price unit trước tính. Blank không là0; không cộng tỷ lệ/đơn giá/snapshot.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="63" customHeight="1">
